--- a/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SBC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SBC.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -515,16 +515,16 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,17 +539,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -567,36 +567,36 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -619,31 +619,31 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -671,41 +671,93 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SBC_M._MBOUP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Mboup</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -786,74 +838,74 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66.8</v>
+        <v>98.7</v>
       </c>
       <c r="E2" t="n">
-        <v>84.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="F2" t="n">
-        <v>85</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Best defense</t>
+          <t>Most used</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>D. Hall | M. Tavares</t>
+          <t>D. Hall | M. Tavares | M. Terry</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>87.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>84.2</v>
+        <v>82</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>trio</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Most used</t>
+          <t>Best defense</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>D. Hall | M. Tavares | M. Terry</t>
+          <t>D. Hall | T. Espada</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>88.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>86.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="5">
@@ -869,20 +921,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M. Tavares | T. Espada</t>
+          <t>D. Hall | T. Espada</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>92.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>85.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>6.9</v>
+        <v>10.8</v>
       </c>
     </row>
   </sheetData>
@@ -1019,7 +1071,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Nongo | D. Hall | M. Tavares | M. Terry | T. Espada (9.5 net)</t>
+          <t>A. Nongo | D. Hall | M. Tavares | M. Terry | T. Espada (17.7 net)</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1105,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
     </row>
@@ -1112,16 +1164,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.6</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="3">
@@ -1131,16 +1183,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>111.8</v>
+        <v>102.9</v>
       </c>
       <c r="C3" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4">
@@ -1150,16 +1202,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>114.2</v>
+        <v>104.8</v>
       </c>
       <c r="C4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>16.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5">
@@ -1169,16 +1221,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.4</v>
+        <v>-1.9</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="6">
@@ -1188,16 +1240,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.5</v>
+        <v>16.3</v>
       </c>
       <c r="C6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
@@ -1232,7 +1284,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>-0</v>
@@ -1245,16 +1297,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="10">
@@ -1270,10 +1322,10 @@
         <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1289,7 +1341,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -1333,7 +1385,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Below-average pace; they are more comfortable when the game stays organized in the half court.</t>
+          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1433,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1487,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control the rhythm: they are more comfortable in a controlled half-court game, so do not let them play cleanly into structure.</t>
+          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1523,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Load into M. Terry: he is the main organizer, so make secondary creators finish possessions.</t>
+          <t>Know the first reference: M. Terry is a paint finisher, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with M. Tavares and M. Terry; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with T. Espada, M. Tavares, and M. Terry; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1589,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from M. Terry and A. Nongo; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from M. Tavares and M. Terry; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially M. Terry, D. Hall, and M. Tavares; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially D. Hall, M. Terry, and M. Tavares; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1625,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: M. Tavares | M. Terry and D. Hall | M. Tavares.</t>
+          <t>Recognize the main duo/trio combinations: M. Tavares | M. Terry and D. Hall | M. Tavares | M. Terry.</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1649,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Do not lose M. Tavares and M. Terry in help-and-recover situations.</t>
+          <t>Do not lose T. Espada and M. Tavares in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1622,7 +1674,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1679,17 +1731,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37.8</v>
+        <v>36.8</v>
       </c>
       <c r="D2" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1715,17 +1767,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>27.3</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1735,7 +1787,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>primary handler</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1751,10 +1803,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31.9</v>
+        <v>34.6</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1783,17 +1835,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.1</v>
+        <v>26.6</v>
       </c>
       <c r="D5" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1804,6 +1856,38 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SBC_M._MBOUP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Mboup</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1917,32 +2001,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_T._ESPADA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>T. Espada</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1963,36 +2047,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -2004,7 +2088,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2018,20 +2102,20 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="H4" t="n">
         <v>1.1</v>
@@ -2055,36 +2139,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SBC_A._NONGO</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Nongo</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2096,74 +2180,94 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>35</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>68.6%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>29.2%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SBC_M._TERRY</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>M. Terry</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>56</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>33</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>57.6%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>27.5%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SBC_A._NONGO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A. Nongo</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2181,23 +2285,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
     </row>
@@ -2217,23 +2321,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -2253,42 +2357,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SBC_M._TERRY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>M. Terry</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -2297,42 +2393,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SBC_D._HALL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>D. Hall</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -2341,23 +2429,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2457,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_D._HALL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>D. Hall</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2385,23 +2473,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2501,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SBC_T._ESPADA</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T. Espada</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2429,23 +2517,155 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SBC_M._TAVARES</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M. Tavares</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>46.2%</t>
+      <c r="K15" t="n">
+        <v>16</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SBC_T._ESPADA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>T. Espada</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SBC_H._SMITH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>H. Smith</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
